--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/may-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/may-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15.72</v>
+        <v>706.84</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>216.109</v>
+        <v>9717.25</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>28.522</v>
+        <v>1282.48</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>830.474</v>
+        <v>37341.92</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>702.08</v>
+        <v>31568.74</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>229.273</v>
+        <v>10309.17</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7990.548</v>
+        <v>359291.68</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>587.992</v>
+        <v>26438.82</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>178.811</v>
+        <v>8040.16</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>26.068</v>
+        <v>1172.14</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>229.273</v>
+        <v>10309.17</v>
       </c>
     </row>
     <row r="13">
@@ -1240,11 +1240,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3529.73754</v>
+        <v>158713.19</v>
       </c>
     </row>
     <row r="14">
@@ -1301,11 +1301,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>209.527</v>
+        <v>9421.290000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>161.259</v>
+        <v>7250.94</v>
       </c>
     </row>
     <row r="16">
@@ -1423,11 +1423,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>78.053</v>
+        <v>3509.62</v>
       </c>
     </row>
   </sheetData>
